--- a/Test.xlsx
+++ b/Test.xlsx
@@ -8,6 +8,10 @@
   <sheets>
     <sheet name="nodes" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="sim" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="power" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="FV" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Carea" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Darea" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -17,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
   <si>
     <t xml:space="preserve">Node ID</t>
   </si>
@@ -163,6 +167,12 @@
     <t>eccentricity</t>
   </si>
   <si>
+    <t>Inclination</t>
+  </si>
+  <si>
+    <t>deg</t>
+  </si>
+  <si>
     <t>LTAN</t>
   </si>
   <si>
@@ -172,9 +182,6 @@
     <t>RAAN</t>
   </si>
   <si>
-    <t>deg</t>
-  </si>
-  <si>
     <t>AOP</t>
   </si>
   <si>
@@ -211,16 +218,19 @@
     <t xml:space="preserve">0=no, 1=yes</t>
   </si>
   <si>
+    <t xml:space="preserve">Power sim</t>
+  </si>
+  <si>
     <t xml:space="preserve">Battery Min.Temp</t>
   </si>
   <si>
     <t xml:space="preserve">Start attitude</t>
   </si>
   <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S=Sun, N=Nadir, R=Random, C=Custom</t>
+    <t>N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S=Sun, N=Nadir, R=Random, C=Custom, F=Fixed</t>
   </si>
   <si>
     <t xml:space="preserve">Random coeff</t>
@@ -229,24 +239,91 @@
     <t xml:space="preserve">if 10 random deg/s is between 0-10, if 1 random deg/s is between 0-1</t>
   </si>
   <si>
-    <t xml:space="preserve">R custom</t>
+    <t xml:space="preserve">X custom</t>
   </si>
   <si>
     <t>deg/s</t>
   </si>
   <si>
-    <t xml:space="preserve">T custom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H custom</t>
+    <t xml:space="preserve">Y custom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z custom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X fixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y fixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z fixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pointing node ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solar cell area</t>
+  </si>
+  <si>
+    <t>cm2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solar cell eff</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPS Charge eff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPS Discharge eff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solar array eff.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Battery capacity</t>
+  </si>
+  <si>
+    <t>Wh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting battery capacity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heater power</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solar cell alpha coeff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solar cell eps coeff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battery max charge power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battery max discharge power</t>
+  </si>
+  <si>
+    <t>mm2</t>
+  </si>
+  <si>
+    <t>mm</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy h:mm"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -263,12 +340,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor theme="7" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0"/>
+        <bgColor theme="9" tint="0"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -298,7 +387,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -332,9 +421,23 @@
       <alignment horizontal="left"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1325,10 +1428,10 @@
         <v>2</v>
       </c>
       <c r="C14" s="4">
-        <v>0.90000000000000002</v>
+        <v>0.59999999999999998</v>
       </c>
       <c r="D14" s="8">
-        <v>0.90000000000000002</v>
+        <v>0.59999999999999998</v>
       </c>
       <c r="E14" s="4">
         <v>915</v>
@@ -1422,7 +1525,7 @@
       <c r="B5" s="10">
         <v>273</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="12" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1450,7 +1553,7 @@
         <v>48</v>
       </c>
       <c r="B8" s="10">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
         <v>49</v>
@@ -1461,7 +1564,7 @@
         <v>50</v>
       </c>
       <c r="B9" s="10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
         <v>51</v>
@@ -1475,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" ht="14.25">
@@ -1486,7 +1589,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" ht="14.25">
@@ -1494,7 +1597,10 @@
         <v>54</v>
       </c>
       <c r="B12" s="10">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="13" ht="14.25">
@@ -1502,43 +1608,40 @@
         <v>55</v>
       </c>
       <c r="B13" s="10">
-        <v>5</v>
-      </c>
-      <c r="C13" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="14.25">
       <c r="A14" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="10">
+        <v>5</v>
+      </c>
+      <c r="C14" t="s">
         <v>57</v>
-      </c>
-      <c r="B14" s="10">
-        <v>25</v>
-      </c>
-      <c r="C14" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="15" ht="14.25">
       <c r="A15" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="10">
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
         <v>59</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="16" ht="14.25">
       <c r="A16" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="10">
-        <v>80</v>
-      </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" ht="14.25">
@@ -1546,62 +1649,62 @@
         <v>62</v>
       </c>
       <c r="B17" s="10">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" ht="14.25">
       <c r="A18" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="10">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
         <v>64</v>
-      </c>
-      <c r="B18" s="10">
-        <v>0</v>
-      </c>
-      <c r="C18" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="19" ht="14.25">
       <c r="A19" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" t="s">
-        <v>67</v>
+      <c r="B19" s="10">
+        <v>1</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="20" ht="14.25">
       <c r="A20" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B20" s="10">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" ht="14.25">
       <c r="A21" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="B21" s="10">
-        <v>3</v>
+        <v>67</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" ht="14.25">
       <c r="A22" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B22" s="10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C22" t="s">
         <v>71</v>
@@ -1609,13 +1712,1416 @@
     </row>
     <row r="23" ht="14.25">
       <c r="A23" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="10">
+        <v>3</v>
+      </c>
+      <c r="C23" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="10">
+    </row>
+    <row r="24" ht="14.25">
+      <c r="A24" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" s="10">
         <v>5</v>
       </c>
-      <c r="C23" t="s">
-        <v>71</v>
+      <c r="C24" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="A25" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" s="10">
+        <v>5</v>
+      </c>
+      <c r="C25" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="A26" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B26" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25">
+      <c r="A27" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B27" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25">
+      <c r="A28" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B28" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25">
+      <c r="A29" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" style="9" width="27.421875"/>
+    <col min="2" max="2" style="1" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="1">
+        <f>8*4</f>
+        <v>32</v>
+      </c>
+      <c r="C1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="C3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="C4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="C5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="1">
+        <v>90</v>
+      </c>
+      <c r="C6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="1">
+        <v>90</v>
+      </c>
+      <c r="C7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="1">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.90000000000000002</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0.90000000000000002</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="1">
+        <f>13*6.66</f>
+        <v>86.579999999999998</v>
+      </c>
+      <c r="C11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" s="1">
+        <v>100</v>
+      </c>
+      <c r="C12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="13" style="1" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.25">
+      <c r="A1" s="4">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="O1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25">
+      <c r="A2" s="15"/>
+      <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="O2" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25">
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="O3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="O4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25">
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="O5" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25">
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="O6" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="16">
+        <v>0.21428571428571427</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8" s="15"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="4">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="16">
+        <v>0.21428571428571427</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9" s="15"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="4">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="16">
+        <v>0.21428571428571427</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="4">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="16">
+        <v>0.21428571428571427</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="4">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4"/>
+      <c r="M11" s="16">
+        <v>7.1428571428571425e-002</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12" s="15"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="4">
+        <v>0</v>
+      </c>
+      <c r="M12" s="16">
+        <v>7.1428571428571425e-002</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="4">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="A15" s="1">
+        <v>1</v>
+      </c>
+      <c r="B15" s="1">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1">
+        <v>4</v>
+      </c>
+      <c r="E15" s="1">
+        <v>5</v>
+      </c>
+      <c r="F15" s="1">
+        <v>6</v>
+      </c>
+      <c r="G15" s="1">
+        <v>7</v>
+      </c>
+      <c r="H15" s="1">
+        <v>8</v>
+      </c>
+      <c r="I15" s="1">
+        <v>9</v>
+      </c>
+      <c r="J15" s="1">
+        <v>10</v>
+      </c>
+      <c r="K15" s="1">
+        <v>11</v>
+      </c>
+      <c r="L15" s="1">
+        <v>12</v>
+      </c>
+      <c r="M15" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="M17" s="1"/>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="J18" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="13" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.25">
+      <c r="A1" s="4">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4">
+        <f>300*1</f>
+        <v>300</v>
+      </c>
+      <c r="D1" s="4">
+        <v>300</v>
+      </c>
+      <c r="E1" s="4">
+        <v>50</v>
+      </c>
+      <c r="F1" s="4">
+        <v>50</v>
+      </c>
+      <c r="G1" s="4">
+        <v>30000</v>
+      </c>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4">
+        <v>50</v>
+      </c>
+      <c r="L1" s="4">
+        <v>50</v>
+      </c>
+      <c r="M1" s="4"/>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25">
+      <c r="A2" s="15"/>
+      <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>300</v>
+      </c>
+      <c r="D2" s="4">
+        <v>300</v>
+      </c>
+      <c r="E2" s="4">
+        <v>50</v>
+      </c>
+      <c r="F2" s="4">
+        <v>50</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4">
+        <v>30000</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4">
+        <v>50</v>
+      </c>
+      <c r="L2" s="4">
+        <v>50</v>
+      </c>
+      <c r="M2" s="4"/>
+      <c r="N2" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25">
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4">
+        <v>50</v>
+      </c>
+      <c r="F3" s="4">
+        <v>50</v>
+      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4">
+        <v>30000</v>
+      </c>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4">
+        <v>50</v>
+      </c>
+      <c r="L3" s="4">
+        <v>50</v>
+      </c>
+      <c r="M3" s="4"/>
+      <c r="N3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <v>50</v>
+      </c>
+      <c r="F4" s="4">
+        <v>50</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4">
+        <v>30000</v>
+      </c>
+      <c r="K4" s="4">
+        <v>50</v>
+      </c>
+      <c r="L4" s="4">
+        <v>50</v>
+      </c>
+      <c r="M4" s="4"/>
+      <c r="N4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25">
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4">
+        <f>100*100</f>
+        <v>10000</v>
+      </c>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25">
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4">
+        <v>10000</v>
+      </c>
+      <c r="M6" s="4"/>
+      <c r="N6" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4">
+        <f t="shared" ref="M7:M10" si="4">100*1</f>
+        <v>100</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8" s="15"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="4">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9" s="15"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="4">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="4">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="4">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12" s="15"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="4">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4"/>
+      <c r="N12" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="4">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="A15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" min="1" max="13" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="18">
+        <v>50</v>
+      </c>
+      <c r="D1" s="18">
+        <v>50</v>
+      </c>
+      <c r="E1" s="18">
+        <v>150</v>
+      </c>
+      <c r="F1" s="18">
+        <v>150</v>
+      </c>
+      <c r="G1" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="18">
+        <v>150</v>
+      </c>
+      <c r="L1" s="18">
+        <v>150</v>
+      </c>
+      <c r="M1" s="4"/>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="18">
+        <v>50</v>
+      </c>
+      <c r="D2" s="18">
+        <v>50</v>
+      </c>
+      <c r="E2" s="18">
+        <v>150</v>
+      </c>
+      <c r="F2" s="18">
+        <v>150</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="18">
+        <v>150</v>
+      </c>
+      <c r="L2" s="18">
+        <v>150</v>
+      </c>
+      <c r="M2" s="4"/>
+      <c r="N2" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18">
+        <v>50</v>
+      </c>
+      <c r="B3" s="18">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="18">
+        <v>150</v>
+      </c>
+      <c r="F3" s="18">
+        <v>150</v>
+      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="J3" s="4"/>
+      <c r="K3" s="18">
+        <v>150</v>
+      </c>
+      <c r="L3" s="18">
+        <v>150</v>
+      </c>
+      <c r="M3" s="4"/>
+      <c r="N3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18">
+        <v>50</v>
+      </c>
+      <c r="B4" s="18">
+        <v>50</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="18">
+        <v>150</v>
+      </c>
+      <c r="F4" s="18">
+        <v>150</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="K4" s="18">
+        <v>150</v>
+      </c>
+      <c r="L4" s="18">
+        <v>150</v>
+      </c>
+      <c r="M4" s="4"/>
+      <c r="N4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18">
+        <v>50</v>
+      </c>
+      <c r="B5" s="18">
+        <v>50</v>
+      </c>
+      <c r="C5" s="18">
+        <v>50</v>
+      </c>
+      <c r="D5" s="18">
+        <v>50</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18">
+        <v>50</v>
+      </c>
+      <c r="B6" s="18">
+        <v>50</v>
+      </c>
+      <c r="C6" s="18">
+        <v>50</v>
+      </c>
+      <c r="D6" s="18">
+        <v>50</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="M6" s="4"/>
+      <c r="N6" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4"/>
+      <c r="B8" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18">
+        <v>50</v>
+      </c>
+      <c r="B11" s="18">
+        <v>50</v>
+      </c>
+      <c r="C11" s="18">
+        <v>50</v>
+      </c>
+      <c r="D11" s="18">
+        <v>50</v>
+      </c>
+      <c r="E11" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18">
+        <v>50</v>
+      </c>
+      <c r="B12" s="18">
+        <v>50</v>
+      </c>
+      <c r="C12" s="18">
+        <v>50</v>
+      </c>
+      <c r="D12" s="18">
+        <v>50</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4"/>
+      <c r="N12" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="18">
+        <v>50</v>
+      </c>
+      <c r="H13" s="18">
+        <v>50</v>
+      </c>
+      <c r="I13" s="18">
+        <v>50</v>
+      </c>
+      <c r="J13" s="18">
+        <v>50</v>
+      </c>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N15" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/Test.xlsx
+++ b/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\piral\Documents\Python\2NDTAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA29E810-3B24-4674-BD28-0BA7CC70807B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B5C7A2-9B33-4FB0-BCA8-8817FDAB7409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nodes" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="106">
   <si>
     <t>Node ID</t>
   </si>
@@ -333,9 +333,6 @@
     <t>mm</t>
   </si>
   <si>
-    <t>S</t>
-  </si>
-  <si>
     <t>Node thermical conduction k W/(m*K)</t>
   </si>
   <si>
@@ -351,7 +348,16 @@
     <t>X,Y,Z if F</t>
   </si>
   <si>
+    <t>N</t>
+  </si>
+  <si>
     <t>Power [W]</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Attitude change time</t>
   </si>
 </sst>
 </file>
@@ -454,7 +460,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -506,6 +512,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -760,7 +768,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>5</v>
@@ -1303,10 +1311,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.33203125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="7" customWidth="1"/>
     <col min="2" max="2" width="18.6640625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1397,7 +1405,7 @@
         <v>50</v>
       </c>
       <c r="B9" s="8">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
         <v>51</v>
@@ -1441,7 +1449,7 @@
         <v>55</v>
       </c>
       <c r="B13" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -1449,7 +1457,7 @@
         <v>56</v>
       </c>
       <c r="B14" s="8">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="C14" t="s">
         <v>57</v>
@@ -1525,8 +1533,8 @@
       <c r="A21" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B21" s="20" t="s">
-        <v>97</v>
+      <c r="B21" s="22" t="s">
+        <v>104</v>
       </c>
       <c r="C21" t="s">
         <v>68</v>
@@ -1589,7 +1597,7 @@
         <v>76</v>
       </c>
       <c r="B27" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -1597,7 +1605,7 @@
         <v>77</v>
       </c>
       <c r="B28" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -1606,6 +1614,17 @@
       </c>
       <c r="B29" s="8" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="B30" s="8">
+        <v>60</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1648,13 +1667,13 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B3" s="1">
         <v>-1.5E-3</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2943,18 +2962,22 @@
   <sheetData>
     <row r="1" spans="1:3" s="18" customFormat="1" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>68</v>
       </c>
       <c r="C1" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="B2" s="21" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
       <c r="C2" s="15"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2979,7 +3002,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>0</v>
@@ -2990,11 +3013,11 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
-      <c r="B2" s="19"/>
+      <c r="B2" s="21"/>
       <c r="C2" s="15"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
+      <c r="A3" s="21"/>
       <c r="B3" s="15"/>
       <c r="C3" s="15"/>
     </row>

--- a/Test.xlsx
+++ b/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\piral\Documents\Python\2NDTAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B5C7A2-9B33-4FB0-BCA8-8817FDAB7409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B30328E9-5C32-43BA-BF5F-B659014CA952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nodes" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="Darea" sheetId="6" r:id="rId6"/>
     <sheet name="Attitude mission" sheetId="7" r:id="rId7"/>
     <sheet name="Power mission" sheetId="8" r:id="rId8"/>
+    <sheet name="Utils" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="137">
   <si>
     <t>Node ID</t>
   </si>
@@ -75,9 +76,6 @@
     <t># Cells</t>
   </si>
   <si>
-    <t>Battery Node</t>
-  </si>
-  <si>
     <t>X+</t>
   </si>
   <si>
@@ -354,10 +352,106 @@
     <t>Power [W]</t>
   </si>
   <si>
-    <t>F</t>
-  </si>
-  <si>
     <t>Attitude change time</t>
+  </si>
+  <si>
+    <t>materiale</t>
+  </si>
+  <si>
+    <t>alpha</t>
+  </si>
+  <si>
+    <t>epsilon</t>
+  </si>
+  <si>
+    <t>Black PCB</t>
+  </si>
+  <si>
+    <t>Green PCB</t>
+  </si>
+  <si>
+    <t>White PCB</t>
+  </si>
+  <si>
+    <t>FR4 no color</t>
+  </si>
+  <si>
+    <t>Copper</t>
+  </si>
+  <si>
+    <t>ENIG</t>
+  </si>
+  <si>
+    <t>HASL</t>
+  </si>
+  <si>
+    <t>Aluminum</t>
+  </si>
+  <si>
+    <t>Black anodized</t>
+  </si>
+  <si>
+    <t>Clear anodized</t>
+  </si>
+  <si>
+    <t>Solar cells</t>
+  </si>
+  <si>
+    <t>Kapton</t>
+  </si>
+  <si>
+    <t>Cs</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>Aluminum 6061-T6</t>
+  </si>
+  <si>
+    <t>Aluminum 7075-T73</t>
+  </si>
+  <si>
+    <t>Steel</t>
+  </si>
+  <si>
+    <t>Titanium</t>
+  </si>
+  <si>
+    <t>FR4</t>
+  </si>
+  <si>
+    <t>average FR4</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>M1.5</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>Area cm2</t>
+  </si>
+  <si>
+    <t># screws</t>
+  </si>
+  <si>
+    <t>sum</t>
+  </si>
+  <si>
+    <t>REP</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>Battery Node (1)</t>
   </si>
 </sst>
 </file>
@@ -368,11 +462,25 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
     <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -398,7 +506,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -417,8 +525,14 @@
         <bgColor theme="9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor theme="9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -456,19 +570,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -478,7 +605,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -497,28 +624,46 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -768,7 +913,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>5</v>
@@ -789,27 +934,27 @@
         <v>10</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>11</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="4">
         <v>0.1</v>
       </c>
       <c r="C2" s="4">
-        <v>0.9</v>
+        <v>0.27</v>
       </c>
       <c r="D2" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="E2" s="4">
-        <v>915</v>
-      </c>
-      <c r="F2" s="4">
-        <v>237</v>
+        <v>0.87</v>
+      </c>
+      <c r="E2" s="15">
+        <v>1200</v>
+      </c>
+      <c r="F2" s="15">
+        <v>10</v>
       </c>
       <c r="G2" s="4">
         <f t="shared" ref="G2:G5" si="0">10*30</f>
@@ -819,10 +964,10 @@
         <v>0</v>
       </c>
       <c r="I2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="K2" s="4">
         <v>1</v>
@@ -834,22 +979,22 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" s="4">
         <v>0.1</v>
       </c>
       <c r="C3" s="4">
-        <v>0.9</v>
+        <v>0.27</v>
       </c>
       <c r="D3" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="E3" s="4">
-        <v>915</v>
-      </c>
-      <c r="F3" s="4">
-        <v>237</v>
+        <v>0.87</v>
+      </c>
+      <c r="E3" s="15">
+        <v>1200</v>
+      </c>
+      <c r="F3" s="15">
+        <v>10</v>
       </c>
       <c r="G3" s="4">
         <f t="shared" si="0"/>
@@ -859,10 +1004,10 @@
         <v>0</v>
       </c>
       <c r="I3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>16</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="K3" s="4">
         <v>1</v>
@@ -874,22 +1019,22 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="4">
         <v>0.1</v>
       </c>
       <c r="C4" s="4">
-        <v>0.9</v>
+        <v>0.27</v>
       </c>
       <c r="D4" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="E4" s="4">
-        <v>915</v>
-      </c>
-      <c r="F4" s="4">
-        <v>237</v>
+        <v>0.87</v>
+      </c>
+      <c r="E4" s="15">
+        <v>1200</v>
+      </c>
+      <c r="F4" s="15">
+        <v>10</v>
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
@@ -899,10 +1044,10 @@
         <v>0</v>
       </c>
       <c r="I4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>20</v>
       </c>
       <c r="K4" s="4">
         <v>1</v>
@@ -914,22 +1059,22 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5" s="6">
         <v>0.1</v>
       </c>
       <c r="C5" s="4">
-        <v>0.9</v>
+        <v>0.27</v>
       </c>
       <c r="D5" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="E5" s="4">
-        <v>915</v>
-      </c>
-      <c r="F5" s="4">
-        <v>237</v>
+        <v>0.87</v>
+      </c>
+      <c r="E5" s="15">
+        <v>1200</v>
+      </c>
+      <c r="F5" s="15">
+        <v>10</v>
       </c>
       <c r="G5" s="4">
         <f t="shared" si="0"/>
@@ -939,10 +1084,10 @@
         <v>0</v>
       </c>
       <c r="I5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>23</v>
       </c>
       <c r="K5" s="4">
         <v>1</v>
@@ -954,22 +1099,22 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="4">
         <v>0.1</v>
       </c>
       <c r="C6" s="4">
-        <v>0.9</v>
+        <v>0.27</v>
       </c>
       <c r="D6" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="E6" s="4">
-        <v>915</v>
-      </c>
-      <c r="F6" s="4">
-        <v>237</v>
+        <v>0.87</v>
+      </c>
+      <c r="E6" s="15">
+        <v>1200</v>
+      </c>
+      <c r="F6" s="15">
+        <v>10</v>
       </c>
       <c r="G6" s="4">
         <f t="shared" ref="G6:G7" si="1">10*10</f>
@@ -979,10 +1124,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="K6" s="4">
         <v>1</v>
@@ -994,22 +1139,22 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7" s="4">
         <v>0.1</v>
       </c>
       <c r="C7" s="4">
-        <v>0.9</v>
+        <v>0.94</v>
       </c>
       <c r="D7" s="4">
         <v>0.9</v>
       </c>
-      <c r="E7" s="4">
-        <v>915</v>
-      </c>
-      <c r="F7" s="4">
-        <v>237</v>
+      <c r="E7" s="15">
+        <v>1200</v>
+      </c>
+      <c r="F7" s="15">
+        <v>10</v>
       </c>
       <c r="G7" s="4">
         <f t="shared" si="1"/>
@@ -1019,10 +1164,10 @@
         <v>0</v>
       </c>
       <c r="I7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="K7" s="4">
         <v>1</v>
@@ -1034,35 +1179,34 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" s="4">
         <v>0.1</v>
       </c>
       <c r="C8" s="4">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="D8" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="E8" s="4">
-        <v>915</v>
-      </c>
-      <c r="F8" s="4">
-        <v>237</v>
+        <v>0.87</v>
+      </c>
+      <c r="E8" s="15">
+        <v>896</v>
+      </c>
+      <c r="F8" s="15">
+        <v>167</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" ref="G8:G11" si="2">10*30</f>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H8" s="4">
         <v>0</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>14</v>
+      <c r="I8" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="J8" s="28" t="s">
+        <v>36</v>
       </c>
       <c r="K8" s="4">
         <v>1</v>
@@ -1072,35 +1216,34 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="4">
         <v>0.1</v>
       </c>
       <c r="C9" s="4">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="D9" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="E9" s="4">
-        <v>915</v>
-      </c>
-      <c r="F9" s="4">
-        <v>237</v>
+        <v>0.87</v>
+      </c>
+      <c r="E9" s="15">
+        <v>896</v>
+      </c>
+      <c r="F9" s="15">
+        <v>167</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="2"/>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H9" s="4">
         <v>0</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>17</v>
+      <c r="I9" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="J9" s="28" t="s">
+        <v>36</v>
       </c>
       <c r="K9" s="4">
         <v>1</v>
@@ -1110,35 +1253,34 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="4">
         <v>0.1</v>
       </c>
       <c r="C10" s="4">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="D10" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="E10" s="4">
-        <v>915</v>
-      </c>
-      <c r="F10" s="4">
-        <v>237</v>
+        <v>0.87</v>
+      </c>
+      <c r="E10" s="15">
+        <v>896</v>
+      </c>
+      <c r="F10" s="15">
+        <v>167</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="2"/>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H10" s="4">
         <v>0</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>20</v>
+      <c r="I10" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10" s="28" t="s">
+        <v>36</v>
       </c>
       <c r="K10" s="4">
         <v>1</v>
@@ -1148,35 +1290,34 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="4">
         <v>0.1</v>
       </c>
       <c r="C11" s="4">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="D11" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="E11" s="4">
-        <v>915</v>
-      </c>
-      <c r="F11" s="4">
-        <v>237</v>
+        <v>0.87</v>
+      </c>
+      <c r="E11" s="15">
+        <v>896</v>
+      </c>
+      <c r="F11" s="15">
+        <v>167</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="2"/>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H11" s="4">
         <v>0</v>
       </c>
-      <c r="I11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>23</v>
+      <c r="I11" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="J11" s="28" t="s">
+        <v>36</v>
       </c>
       <c r="K11" s="4">
         <v>1</v>
@@ -1186,35 +1327,34 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="4">
         <v>0.1</v>
       </c>
       <c r="C12" s="4">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="D12" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="E12" s="4">
-        <v>915</v>
-      </c>
-      <c r="F12" s="4">
-        <v>237</v>
+        <v>0.87</v>
+      </c>
+      <c r="E12" s="15">
+        <v>896</v>
+      </c>
+      <c r="F12" s="15">
+        <v>167</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" ref="G12:G13" si="3">10*10</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H12" s="4">
         <v>0</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>26</v>
+      <c r="I12" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12" s="28" t="s">
+        <v>36</v>
       </c>
       <c r="K12" s="4">
         <v>1</v>
@@ -1224,35 +1364,34 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="4">
         <v>0.1</v>
       </c>
       <c r="C13" s="4">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="D13" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="E13" s="4">
-        <v>915</v>
-      </c>
-      <c r="F13" s="4">
-        <v>237</v>
+        <v>0.87</v>
+      </c>
+      <c r="E13" s="15">
+        <v>896</v>
+      </c>
+      <c r="F13" s="15">
+        <v>167</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="3"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H13" s="4">
         <v>0</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>29</v>
+      <c r="I13" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="J13" s="28" t="s">
+        <v>36</v>
       </c>
       <c r="K13" s="4">
         <v>1</v>
@@ -1262,22 +1401,22 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" s="4">
         <v>2</v>
       </c>
       <c r="C14" s="4">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="D14" s="4">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E14" s="4">
-        <v>915</v>
+        <v>1000</v>
       </c>
       <c r="F14" s="4">
-        <v>237</v>
+        <v>130</v>
       </c>
       <c r="G14" s="4">
         <v>0</v>
@@ -1286,13 +1425,13 @@
         <v>6</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K14" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
@@ -1320,40 +1459,40 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1" s="9">
         <v>46101.5</v>
       </c>
       <c r="C1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2" s="8">
         <v>6371</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="8">
         <v>1367</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B4" s="8">
         <v>0.3</v>
@@ -1361,29 +1500,29 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5" s="8">
         <v>237</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B6" s="8">
         <v>550</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B7" s="8">
         <v>1E-3</v>
@@ -1391,202 +1530,202 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" s="8">
         <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="8">
+        <v>14.5</v>
+      </c>
+      <c r="C9" t="s">
         <v>50</v>
-      </c>
-      <c r="B9" s="8">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B10" s="8">
         <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B11" s="8">
         <v>0</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B12" s="8">
         <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="8">
+        <v>60</v>
+      </c>
+      <c r="C14" t="s">
         <v>56</v>
-      </c>
-      <c r="B14" s="8">
-        <v>10</v>
-      </c>
-      <c r="C14" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B15" s="8">
         <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>61</v>
-      </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B17" s="8">
         <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B18" s="8">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B19" s="8">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B20" s="8">
         <v>0</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" t="s">
         <v>67</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="C21" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B22" s="8">
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B23" s="8">
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B24" s="8">
         <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B25" s="8">
         <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B26" s="8">
         <v>1</v>
@@ -1594,7 +1733,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B27" s="8">
         <v>2</v>
@@ -1602,7 +1741,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B28" s="8">
         <v>3</v>
@@ -1610,21 +1749,21 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="20" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B30" s="8">
         <v>60</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1644,107 +1783,107 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B1" s="1">
         <f>8*4</f>
         <v>32</v>
       </c>
       <c r="C1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B2" s="1">
         <v>0.3</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B3" s="1">
         <v>-1.5E-3</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B4" s="1">
         <v>0.9</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B5" s="1">
         <v>0.9</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B6" s="1">
         <v>0.9</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B7" s="1">
         <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B8" s="1">
         <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B9" s="1">
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B10" s="1">
         <v>0.9</v>
@@ -1752,7 +1891,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B11" s="1">
         <v>0.9</v>
@@ -1760,25 +1899,25 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B12" s="1">
         <f>13*6.66</f>
         <v>86.58</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B13" s="1">
         <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1812,7 +1951,7 @@
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
       <c r="O1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -1832,7 +1971,7 @@
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="O2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -1852,7 +1991,7 @@
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="O3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
@@ -1872,7 +2011,7 @@
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="O4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
@@ -1892,7 +2031,7 @@
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="O5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
@@ -1912,7 +2051,7 @@
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="O6" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
@@ -1934,7 +2073,7 @@
         <v>0.21428571428571427</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
@@ -1956,7 +2095,7 @@
         <v>0.21428571428571427</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
@@ -1978,7 +2117,7 @@
         <v>0.21428571428571427</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
@@ -2000,7 +2139,7 @@
         <v>0.21428571428571427</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
@@ -2022,7 +2161,7 @@
         <v>7.1428571428571425E-2</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
@@ -2044,7 +2183,7 @@
         <v>7.1428571428571425E-2</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
@@ -2064,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
@@ -2135,26 +2274,22 @@
         <v>300</v>
       </c>
       <c r="E1" s="4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F1" s="4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G1" s="4">
-        <v>30000</v>
+        <v>30.18</v>
       </c>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
-      <c r="K1" s="4">
-        <v>50</v>
-      </c>
-      <c r="L1" s="4">
-        <v>50</v>
-      </c>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
       <c r="M1" s="4"/>
       <c r="N1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -2169,26 +2304,22 @@
         <v>300</v>
       </c>
       <c r="E2" s="4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F2" s="4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4">
-        <v>30000</v>
+        <v>30.18</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
-      <c r="K2" s="4">
-        <v>50</v>
-      </c>
-      <c r="L2" s="4">
-        <v>50</v>
-      </c>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="N2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -2199,26 +2330,22 @@
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F3" s="4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4">
-        <v>30000</v>
+        <v>30.18</v>
       </c>
       <c r="J3" s="4"/>
-      <c r="K3" s="4">
-        <v>50</v>
-      </c>
-      <c r="L3" s="4">
-        <v>50</v>
-      </c>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -2229,26 +2356,22 @@
         <v>0</v>
       </c>
       <c r="E4" s="4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F4" s="4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4">
-        <v>30000</v>
-      </c>
-      <c r="K4" s="4">
-        <v>50</v>
-      </c>
-      <c r="L4" s="4">
-        <v>50</v>
-      </c>
+        <v>30.18</v>
+      </c>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -2265,13 +2388,12 @@
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4">
-        <f>100*100</f>
-        <v>10000</v>
+        <v>20.12</v>
       </c>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -2289,11 +2411,11 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4">
-        <v>10000</v>
+        <v>20.12</v>
       </c>
       <c r="M6" s="4"/>
       <c r="N6" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -2312,11 +2434,10 @@
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4">
-        <f t="shared" ref="M7:M10" si="0">100*1</f>
-        <v>100</v>
+        <v>30.18</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -2335,11 +2456,10 @@
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4">
-        <f t="shared" si="0"/>
-        <v>100</v>
+        <v>30.18</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -2358,11 +2478,10 @@
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4">
-        <f t="shared" si="0"/>
-        <v>100</v>
+        <v>30.18</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -2381,11 +2500,10 @@
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4">
-        <f t="shared" si="0"/>
-        <v>100</v>
+        <v>30.18</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -2405,7 +2523,7 @@
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -2425,7 +2543,7 @@
       </c>
       <c r="M12" s="4"/>
       <c r="N12" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -2445,51 +2563,51 @@
         <v>0</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="K15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="M15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="M15" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="N15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -2529,15 +2647,11 @@
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
-      <c r="K1" s="13">
-        <v>150</v>
-      </c>
-      <c r="L1" s="13">
-        <v>150</v>
-      </c>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
       <c r="M1" s="4"/>
       <c r="N1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -2563,15 +2677,11 @@
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
-      <c r="K2" s="13">
-        <v>150</v>
-      </c>
-      <c r="L2" s="13">
-        <v>150</v>
-      </c>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
       <c r="M2" s="4"/>
       <c r="N2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -2597,15 +2707,11 @@
         <v>0.5</v>
       </c>
       <c r="J3" s="4"/>
-      <c r="K3" s="13">
-        <v>150</v>
-      </c>
-      <c r="L3" s="13">
-        <v>150</v>
-      </c>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
       <c r="M3" s="4"/>
       <c r="N3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -2631,15 +2737,11 @@
       <c r="J4" s="13">
         <v>0.5</v>
       </c>
-      <c r="K4" s="13">
-        <v>150</v>
-      </c>
-      <c r="L4" s="13">
-        <v>150</v>
-      </c>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
       <c r="M4" s="4"/>
       <c r="N4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -2669,7 +2771,7 @@
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -2699,7 +2801,7 @@
       </c>
       <c r="M6" s="4"/>
       <c r="N6" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -2723,7 +2825,7 @@
         <v>0.5</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -2747,7 +2849,7 @@
         <v>0.5</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -2771,7 +2873,7 @@
         <v>0.5</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -2794,22 +2896,14 @@
         <v>0.5</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13">
-        <v>50</v>
-      </c>
-      <c r="B11" s="13">
-        <v>50</v>
-      </c>
-      <c r="C11" s="13">
-        <v>50</v>
-      </c>
-      <c r="D11" s="13">
-        <v>50</v>
-      </c>
+      <c r="A11" s="29"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
       <c r="E11" s="13">
         <v>0.5</v>
       </c>
@@ -2824,22 +2918,14 @@
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13">
-        <v>50</v>
-      </c>
-      <c r="B12" s="13">
-        <v>50</v>
-      </c>
-      <c r="C12" s="13">
-        <v>50</v>
-      </c>
-      <c r="D12" s="13">
-        <v>50</v>
-      </c>
+      <c r="A12" s="29"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
       <c r="E12" s="4"/>
       <c r="F12" s="13">
         <v>0.5</v>
@@ -2854,7 +2940,7 @@
       </c>
       <c r="M12" s="4"/>
       <c r="N12" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -2882,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -2902,46 +2988,46 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="K15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="M15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="M15" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="N15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -2952,7 +3038,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B46D2C0-A102-402C-B1A9-63B7B9D98B3D}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.5546875" style="1" customWidth="1"/>
@@ -2962,28 +3048,37 @@
   <sheetData>
     <row r="1" spans="1:3" s="18" customFormat="1" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>100</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>102</v>
+        <v>0.3</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>101</v>
       </c>
       <c r="C2" s="15"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
+      <c r="A3" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>135</v>
+      </c>
       <c r="C3" s="15"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>134</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3002,13 +3097,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -3024,4 +3119,324 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A78FF1-23BD-4EE4-8957-AB041A8C157D}">
+  <dimension ref="C2:M20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="26.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="1"/>
+    <col min="7" max="7" width="24" style="1" customWidth="1"/>
+    <col min="8" max="9" width="8.88671875" style="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C2" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C3" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="15">
+        <v>0.94</v>
+      </c>
+      <c r="E3" s="15">
+        <v>0.9</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="H3" s="15">
+        <v>896</v>
+      </c>
+      <c r="I3" s="15">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C4" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="E4" s="15">
+        <v>0.87</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="H4" s="15">
+        <v>960</v>
+      </c>
+      <c r="I4" s="15">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C5" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="15">
+        <v>0.27</v>
+      </c>
+      <c r="E5" s="15">
+        <v>0.87</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="H5" s="15">
+        <v>385</v>
+      </c>
+      <c r="I5" s="15">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="6" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C6" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" s="15">
+        <v>0.65</v>
+      </c>
+      <c r="E6" s="15">
+        <v>0.82</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="H6" s="15">
+        <v>500</v>
+      </c>
+      <c r="I6" s="15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C7" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" s="15">
+        <v>0.25</v>
+      </c>
+      <c r="E7" s="15">
+        <v>0.04</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="H7" s="15">
+        <v>526</v>
+      </c>
+      <c r="I7" s="15">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="8" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C8" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="E8" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="H8" s="15">
+        <v>1200</v>
+      </c>
+      <c r="I8" s="15">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="9" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C9" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="15">
+        <v>0.45</v>
+      </c>
+      <c r="E9" s="15">
+        <v>0.12</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="H9" s="15">
+        <v>1090</v>
+      </c>
+      <c r="I9" s="15">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="10" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="G10" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="H10" s="15">
+        <v>1200</v>
+      </c>
+      <c r="I10" s="15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C11" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D11" s="15">
+        <v>0.17</v>
+      </c>
+      <c r="E11" s="15">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="12" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C12" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="D12" s="15">
+        <v>0.91</v>
+      </c>
+      <c r="E12" s="15">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="13" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C13" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" s="15">
+        <v>0.22</v>
+      </c>
+      <c r="E13" s="15">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="14" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C14" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="D14" s="15">
+        <v>0.91</v>
+      </c>
+      <c r="E14" s="15">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="15" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C15" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="D15" s="15">
+        <v>0.41</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0.77</v>
+      </c>
+      <c r="J15" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="K15" s="24" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="16" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="I16" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="J16" s="15">
+        <v>0.46</v>
+      </c>
+      <c r="K16" s="27"/>
+      <c r="L16" s="15">
+        <f>J16*K16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="9:13" x14ac:dyDescent="0.3">
+      <c r="I17" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="J17" s="15">
+        <v>1.08</v>
+      </c>
+      <c r="K17" s="27"/>
+      <c r="L17" s="15">
+        <f t="shared" ref="L17:L19" si="0">J17*K17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="9:13" x14ac:dyDescent="0.3">
+      <c r="I18" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="J18" s="15">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="K18" s="27"/>
+      <c r="L18" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="9:13" x14ac:dyDescent="0.3">
+      <c r="I19" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="J19" s="15">
+        <v>5.03</v>
+      </c>
+      <c r="K19" s="15">
+        <v>4</v>
+      </c>
+      <c r="L19" s="15">
+        <f t="shared" si="0"/>
+        <v>20.12</v>
+      </c>
+    </row>
+    <row r="20" spans="9:13" x14ac:dyDescent="0.3">
+      <c r="K20" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="L20" s="26">
+        <f>SUM(L16:L19)</f>
+        <v>20.12</v>
+      </c>
+      <c r="M20" s="24" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>